--- a/load-tests/reports/SpareGrow_Baseline_Load_Test_Report.xlsx
+++ b/load-tests/reports/SpareGrow_Baseline_Load_Test_Report.xlsx
@@ -22,16 +22,16 @@
     <t>SPAREGROW LOAD &amp; PERFORMANCE TEST REPORT (100 CONCURRENT VUs)</t>
   </si>
   <si>
-    <t>Duration: 60s Continuous | Virtual Users: 100 | Total Requests: 149800 | Generated: 2/8/2026, 7:11:38 pm</t>
-  </si>
-  <si>
-    <t>1,49,800</t>
-  </si>
-  <si>
-    <t>2494.6 req/s</t>
-  </si>
-  <si>
-    <t>16.95 ms</t>
+    <t>Duration: 60s Continuous | Virtual Users: 100 | Total Requests: 84455 | Generated: 6/8/2026, 9:09:58 am</t>
+  </si>
+  <si>
+    <t>84,455</t>
+  </si>
+  <si>
+    <t>1405.9 req/s</t>
+  </si>
+  <si>
+    <t>43.15 ms</t>
   </si>
   <si>
     <t>100.0%</t>
@@ -67,7 +67,7 @@
     <t>Total Requests Sent</t>
   </si>
   <si>
-    <t>1,49,800 reqs</t>
+    <t>84,455 reqs</t>
   </si>
   <si>
     <t>Successful Requests (2xx/3xx)</t>
@@ -88,25 +88,25 @@
     <t>Throughput / RPS</t>
   </si>
   <si>
-    <t>2494.6 req/sec</t>
+    <t>1405.9 req/sec</t>
   </si>
   <si>
     <t>Total Data Transferred</t>
   </si>
   <si>
-    <t>3443.56 MB</t>
+    <t>2103.75 MB</t>
   </si>
   <si>
     <t>Fastest Response (Min)</t>
   </si>
   <si>
-    <t>0.64 ms</t>
+    <t>1.43 ms</t>
   </si>
   <si>
     <t>Slowest Response (Max)</t>
   </si>
   <si>
-    <t>125.52 ms</t>
+    <t>213.49 ms</t>
   </si>
   <si>
     <t>Average Response Time</t>
@@ -115,25 +115,25 @@
     <t>Median Response Time (p50)</t>
   </si>
   <si>
-    <t>15.55 ms</t>
+    <t>41.9 ms</t>
   </si>
   <si>
     <t>90th Percentile (p90)</t>
   </si>
   <si>
-    <t>26.47 ms</t>
+    <t>61.56 ms</t>
   </si>
   <si>
     <t>95th Percentile (p95)</t>
   </si>
   <si>
-    <t>32.17 ms</t>
+    <t>70.02 ms</t>
   </si>
   <si>
     <t>99th Percentile (p99)</t>
   </si>
   <si>
-    <t>47.68 ms</t>
+    <t>94.92 ms</t>
   </si>
   <si>
     <t>SLA Compliance Status</t>
@@ -169,7 +169,7 @@
     <t>Minimum (Fastest)</t>
   </si>
   <si>
-    <t>0.0006</t>
+    <t>0.0014</t>
   </si>
   <si>
     <t>&lt; 100 ms</t>
@@ -187,7 +187,7 @@
     <t>50th Percentile (Median)</t>
   </si>
   <si>
-    <t>0.0156</t>
+    <t>0.0419</t>
   </si>
   <si>
     <t>&lt; 200 ms</t>
@@ -199,7 +199,7 @@
     <t>75th Percentile (p75)</t>
   </si>
   <si>
-    <t>0.0200</t>
+    <t>0.0507</t>
   </si>
   <si>
     <t>&lt; 350 ms</t>
@@ -208,7 +208,7 @@
     <t>75% of all requests responded faster than this</t>
   </si>
   <si>
-    <t>0.0265</t>
+    <t>0.0616</t>
   </si>
   <si>
     <t>&lt; 500 ms</t>
@@ -217,7 +217,7 @@
     <t>90% of all requests responded faster than this</t>
   </si>
   <si>
-    <t>0.0322</t>
+    <t>0.0700</t>
   </si>
   <si>
     <t>&lt; 650 ms</t>
@@ -226,7 +226,7 @@
     <t>95% of peak requests served comfortably within SLA</t>
   </si>
   <si>
-    <t>0.0477</t>
+    <t>0.0949</t>
   </si>
   <si>
     <t>&lt; 1200 ms</t>
@@ -238,7 +238,7 @@
     <t>Maximum (Slowest)</t>
   </si>
   <si>
-    <t>0.1255</t>
+    <t>0.2135</t>
   </si>
   <si>
     <t>&lt; 2000 ms</t>
@@ -253,7 +253,7 @@
     <t>Average (Mean)</t>
   </si>
   <si>
-    <t>0.0169</t>
+    <t>0.0432</t>
   </si>
   <si>
     <t>&lt; 250 ms</t>
@@ -382,181 +382,181 @@
     <t>Errors</t>
   </si>
   <si>
-    <t>7:10:39 pm</t>
-  </si>
-  <si>
-    <t>7:10:40 pm</t>
-  </si>
-  <si>
-    <t>7:10:41 pm</t>
-  </si>
-  <si>
-    <t>7:10:42 pm</t>
-  </si>
-  <si>
-    <t>7:10:43 pm</t>
-  </si>
-  <si>
-    <t>7:10:44 pm</t>
-  </si>
-  <si>
-    <t>7:10:45 pm</t>
-  </si>
-  <si>
-    <t>7:10:46 pm</t>
-  </si>
-  <si>
-    <t>7:10:47 pm</t>
-  </si>
-  <si>
-    <t>7:10:48 pm</t>
-  </si>
-  <si>
-    <t>7:10:49 pm</t>
-  </si>
-  <si>
-    <t>7:10:50 pm</t>
-  </si>
-  <si>
-    <t>7:10:51 pm</t>
-  </si>
-  <si>
-    <t>7:10:52 pm</t>
-  </si>
-  <si>
-    <t>7:10:53 pm</t>
-  </si>
-  <si>
-    <t>7:10:54 pm</t>
-  </si>
-  <si>
-    <t>7:10:55 pm</t>
-  </si>
-  <si>
-    <t>7:10:56 pm</t>
-  </si>
-  <si>
-    <t>7:10:57 pm</t>
-  </si>
-  <si>
-    <t>7:10:58 pm</t>
-  </si>
-  <si>
-    <t>7:10:59 pm</t>
-  </si>
-  <si>
-    <t>7:11:00 pm</t>
-  </si>
-  <si>
-    <t>7:11:01 pm</t>
-  </si>
-  <si>
-    <t>7:11:02 pm</t>
-  </si>
-  <si>
-    <t>7:11:03 pm</t>
-  </si>
-  <si>
-    <t>7:11:04 pm</t>
-  </si>
-  <si>
-    <t>7:11:05 pm</t>
-  </si>
-  <si>
-    <t>7:11:06 pm</t>
-  </si>
-  <si>
-    <t>7:11:07 pm</t>
-  </si>
-  <si>
-    <t>7:11:08 pm</t>
-  </si>
-  <si>
-    <t>7:11:09 pm</t>
-  </si>
-  <si>
-    <t>7:11:10 pm</t>
-  </si>
-  <si>
-    <t>7:11:11 pm</t>
-  </si>
-  <si>
-    <t>7:11:12 pm</t>
-  </si>
-  <si>
-    <t>7:11:13 pm</t>
-  </si>
-  <si>
-    <t>7:11:14 pm</t>
-  </si>
-  <si>
-    <t>7:11:15 pm</t>
-  </si>
-  <si>
-    <t>7:11:16 pm</t>
-  </si>
-  <si>
-    <t>7:11:17 pm</t>
-  </si>
-  <si>
-    <t>7:11:18 pm</t>
-  </si>
-  <si>
-    <t>7:11:19 pm</t>
-  </si>
-  <si>
-    <t>7:11:20 pm</t>
-  </si>
-  <si>
-    <t>7:11:21 pm</t>
-  </si>
-  <si>
-    <t>7:11:22 pm</t>
-  </si>
-  <si>
-    <t>7:11:23 pm</t>
-  </si>
-  <si>
-    <t>7:11:24 pm</t>
-  </si>
-  <si>
-    <t>7:11:25 pm</t>
-  </si>
-  <si>
-    <t>7:11:26 pm</t>
-  </si>
-  <si>
-    <t>7:11:27 pm</t>
-  </si>
-  <si>
-    <t>7:11:28 pm</t>
-  </si>
-  <si>
-    <t>7:11:29 pm</t>
-  </si>
-  <si>
-    <t>7:11:30 pm</t>
-  </si>
-  <si>
-    <t>7:11:31 pm</t>
-  </si>
-  <si>
-    <t>7:11:32 pm</t>
-  </si>
-  <si>
-    <t>7:11:33 pm</t>
-  </si>
-  <si>
-    <t>7:11:34 pm</t>
-  </si>
-  <si>
-    <t>7:11:35 pm</t>
-  </si>
-  <si>
-    <t>7:11:36 pm</t>
-  </si>
-  <si>
-    <t>7:11:37 pm</t>
+    <t>9:08:59 am</t>
+  </si>
+  <si>
+    <t>9:09:00 am</t>
+  </si>
+  <si>
+    <t>9:09:01 am</t>
+  </si>
+  <si>
+    <t>9:09:02 am</t>
+  </si>
+  <si>
+    <t>9:09:03 am</t>
+  </si>
+  <si>
+    <t>9:09:04 am</t>
+  </si>
+  <si>
+    <t>9:09:05 am</t>
+  </si>
+  <si>
+    <t>9:09:06 am</t>
+  </si>
+  <si>
+    <t>9:09:07 am</t>
+  </si>
+  <si>
+    <t>9:09:08 am</t>
+  </si>
+  <si>
+    <t>9:09:09 am</t>
+  </si>
+  <si>
+    <t>9:09:10 am</t>
+  </si>
+  <si>
+    <t>9:09:11 am</t>
+  </si>
+  <si>
+    <t>9:09:12 am</t>
+  </si>
+  <si>
+    <t>9:09:13 am</t>
+  </si>
+  <si>
+    <t>9:09:14 am</t>
+  </si>
+  <si>
+    <t>9:09:15 am</t>
+  </si>
+  <si>
+    <t>9:09:16 am</t>
+  </si>
+  <si>
+    <t>9:09:17 am</t>
+  </si>
+  <si>
+    <t>9:09:18 am</t>
+  </si>
+  <si>
+    <t>9:09:19 am</t>
+  </si>
+  <si>
+    <t>9:09:20 am</t>
+  </si>
+  <si>
+    <t>9:09:21 am</t>
+  </si>
+  <si>
+    <t>9:09:22 am</t>
+  </si>
+  <si>
+    <t>9:09:23 am</t>
+  </si>
+  <si>
+    <t>9:09:24 am</t>
+  </si>
+  <si>
+    <t>9:09:25 am</t>
+  </si>
+  <si>
+    <t>9:09:26 am</t>
+  </si>
+  <si>
+    <t>9:09:27 am</t>
+  </si>
+  <si>
+    <t>9:09:28 am</t>
+  </si>
+  <si>
+    <t>9:09:29 am</t>
+  </si>
+  <si>
+    <t>9:09:30 am</t>
+  </si>
+  <si>
+    <t>9:09:31 am</t>
+  </si>
+  <si>
+    <t>9:09:32 am</t>
+  </si>
+  <si>
+    <t>9:09:33 am</t>
+  </si>
+  <si>
+    <t>9:09:34 am</t>
+  </si>
+  <si>
+    <t>9:09:35 am</t>
+  </si>
+  <si>
+    <t>9:09:36 am</t>
+  </si>
+  <si>
+    <t>9:09:37 am</t>
+  </si>
+  <si>
+    <t>9:09:38 am</t>
+  </si>
+  <si>
+    <t>9:09:39 am</t>
+  </si>
+  <si>
+    <t>9:09:40 am</t>
+  </si>
+  <si>
+    <t>9:09:41 am</t>
+  </si>
+  <si>
+    <t>9:09:42 am</t>
+  </si>
+  <si>
+    <t>9:09:43 am</t>
+  </si>
+  <si>
+    <t>9:09:44 am</t>
+  </si>
+  <si>
+    <t>9:09:45 am</t>
+  </si>
+  <si>
+    <t>9:09:46 am</t>
+  </si>
+  <si>
+    <t>9:09:47 am</t>
+  </si>
+  <si>
+    <t>9:09:48 am</t>
+  </si>
+  <si>
+    <t>9:09:49 am</t>
+  </si>
+  <si>
+    <t>9:09:50 am</t>
+  </si>
+  <si>
+    <t>9:09:51 am</t>
+  </si>
+  <si>
+    <t>9:09:52 am</t>
+  </si>
+  <si>
+    <t>9:09:53 am</t>
+  </si>
+  <si>
+    <t>9:09:54 am</t>
+  </si>
+  <si>
+    <t>9:09:55 am</t>
+  </si>
+  <si>
+    <t>9:09:56 am</t>
+  </si>
+  <si>
+    <t>9:09:57 am</t>
   </si>
   <si>
     <t>HTTP STATUS CODE DISTRIBUTION &amp; ERROR RATE ANALYSIS</t>
@@ -610,7 +610,7 @@
     <t>&gt;= 100 req/s</t>
   </si>
   <si>
-    <t>+2394.6 req/s</t>
+    <t>+1305.9 req/s</t>
   </si>
   <si>
     <t>PASSED</t>
@@ -619,7 +619,7 @@
     <t>&lt;= 250 ms</t>
   </si>
   <si>
-    <t>-233.1 ms</t>
+    <t>-206.8 ms</t>
   </si>
   <si>
     <t>95th Percentile Latency</t>
@@ -628,7 +628,7 @@
     <t>&lt;= 500 ms</t>
   </si>
   <si>
-    <t>-467.8 ms</t>
+    <t>-430.0 ms</t>
   </si>
   <si>
     <t>99th Percentile Latency</t>
@@ -637,7 +637,7 @@
     <t>&lt;= 1200 ms</t>
   </si>
   <si>
-    <t>-1152.3 ms</t>
+    <t>-1105.1 ms</t>
   </si>
   <si>
     <t>Max Peak Latency</t>
@@ -646,7 +646,7 @@
     <t>&lt;= 2000 ms</t>
   </si>
   <si>
-    <t>-1874.5 ms</t>
+    <t>-1786.5 ms</t>
   </si>
   <si>
     <t>&lt;= 0.5%</t>
@@ -709,7 +709,7 @@
     <t>Request Processing Capacity</t>
   </si>
   <si>
-    <t>2494.6 requests/sec</t>
+    <t>1405.9 requests/sec</t>
   </si>
   <si>
     <t>Cluster scaling recommended above 500 RPS</t>
@@ -724,7 +724,7 @@
     <t>API Response Time</t>
   </si>
   <si>
-    <t>Avg: 16.95ms, p95: 32.17ms</t>
+    <t>Avg: 43.15ms, p95: 70.02ms</t>
   </si>
   <si>
     <t>Maintain DB connection pooling &lt;= 50ms</t>
@@ -1638,7 +1638,7 @@
         <v>49</v>
       </c>
       <c r="B4" s="15">
-        <v>0.64</v>
+        <v>1.43</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>50</v>
@@ -1661,7 +1661,7 @@
         <v>55</v>
       </c>
       <c r="B5" s="15">
-        <v>15.55</v>
+        <v>41.9</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>56</v>
@@ -1684,7 +1684,7 @@
         <v>59</v>
       </c>
       <c r="B6" s="15">
-        <v>19.98</v>
+        <v>50.7</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>60</v>
@@ -1707,7 +1707,7 @@
         <v>33</v>
       </c>
       <c r="B7" s="15">
-        <v>26.47</v>
+        <v>61.56</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>63</v>
@@ -1730,7 +1730,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="15">
-        <v>32.17</v>
+        <v>70.02</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>66</v>
@@ -1753,7 +1753,7 @@
         <v>37</v>
       </c>
       <c r="B9" s="15">
-        <v>47.68</v>
+        <v>94.92</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>69</v>
@@ -1776,7 +1776,7 @@
         <v>72</v>
       </c>
       <c r="B10" s="15">
-        <v>125.52</v>
+        <v>213.49</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>73</v>
@@ -1799,7 +1799,7 @@
         <v>77</v>
       </c>
       <c r="B11" s="15">
-        <v>16.95</v>
+        <v>43.15</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>78</v>
@@ -1891,25 +1891,25 @@
         <v>94</v>
       </c>
       <c r="D4" s="15">
-        <v>29938</v>
+        <v>16783</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>5</v>
       </c>
       <c r="F4" s="15">
-        <v>0.99</v>
+        <v>1.69</v>
       </c>
       <c r="G4" s="15">
-        <v>17.19</v>
+        <v>43.58</v>
       </c>
       <c r="H4" s="15">
-        <v>30.71</v>
+        <v>62.69</v>
       </c>
       <c r="I4" s="15">
-        <v>95.9</v>
+        <v>171.52</v>
       </c>
       <c r="J4" s="15">
-        <v>22745.9</v>
+        <v>54430</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1923,25 +1923,25 @@
         <v>96</v>
       </c>
       <c r="D5" s="21">
-        <v>22368</v>
+        <v>12729</v>
       </c>
       <c r="E5" s="22" t="s">
         <v>5</v>
       </c>
       <c r="F5" s="21">
-        <v>1.8</v>
+        <v>3.33</v>
       </c>
       <c r="G5" s="21">
-        <v>23.72</v>
+        <v>60.42</v>
       </c>
       <c r="H5" s="21">
-        <v>42.61</v>
+        <v>87.45</v>
       </c>
       <c r="I5" s="21">
-        <v>109.45</v>
+        <v>213.49</v>
       </c>
       <c r="J5" s="21">
-        <v>3352535.1</v>
+        <v>1930867.5</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1955,25 +1955,25 @@
         <v>98</v>
       </c>
       <c r="D6" s="15">
-        <v>15088</v>
+        <v>8465</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>5</v>
       </c>
       <c r="F6" s="15">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="G6" s="15">
-        <v>17.17</v>
+        <v>43.64</v>
       </c>
       <c r="H6" s="15">
-        <v>30.72</v>
+        <v>62.9</v>
       </c>
       <c r="I6" s="15">
-        <v>96.14</v>
+        <v>171.47</v>
       </c>
       <c r="J6" s="15">
-        <v>102624.9</v>
+        <v>57576.9</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1987,25 +1987,25 @@
         <v>100</v>
       </c>
       <c r="D7" s="21">
-        <v>14875</v>
+        <v>8391</v>
       </c>
       <c r="E7" s="22" t="s">
         <v>5</v>
       </c>
       <c r="F7" s="21">
-        <v>0.86</v>
+        <v>2.43</v>
       </c>
       <c r="G7" s="21">
-        <v>17.14</v>
+        <v>43.92</v>
       </c>
       <c r="H7" s="21">
-        <v>30.81</v>
+        <v>63.92</v>
       </c>
       <c r="I7" s="21">
-        <v>125.52</v>
+        <v>171.66</v>
       </c>
       <c r="J7" s="21">
-        <v>11301.5</v>
+        <v>27213.4</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2019,25 +2019,25 @@
         <v>102</v>
       </c>
       <c r="D8" s="15">
-        <v>22601</v>
+        <v>12883</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>5</v>
       </c>
       <c r="F8" s="15">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="G8" s="15">
-        <v>17.14</v>
+        <v>43.8</v>
       </c>
       <c r="H8" s="15">
-        <v>30.59</v>
+        <v>63.21</v>
       </c>
       <c r="I8" s="15">
-        <v>95.97</v>
+        <v>171.58</v>
       </c>
       <c r="J8" s="15">
-        <v>17171.5</v>
+        <v>41781.7</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2051,25 +2051,25 @@
         <v>104</v>
       </c>
       <c r="D9" s="21">
-        <v>15048</v>
+        <v>8428</v>
       </c>
       <c r="E9" s="22" t="s">
         <v>5</v>
       </c>
       <c r="F9" s="21">
-        <v>0.64</v>
+        <v>1.58</v>
       </c>
       <c r="G9" s="21">
-        <v>17.21</v>
+        <v>43.92</v>
       </c>
       <c r="H9" s="21">
-        <v>30.79</v>
+        <v>63.54</v>
       </c>
       <c r="I9" s="21">
-        <v>96.07</v>
+        <v>171.83</v>
       </c>
       <c r="J9" s="21">
-        <v>11433</v>
+        <v>27333.4</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2083,25 +2083,25 @@
         <v>106</v>
       </c>
       <c r="D10" s="15">
-        <v>7469</v>
+        <v>4167</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>5</v>
       </c>
       <c r="F10" s="15">
-        <v>1.63</v>
+        <v>2.21</v>
       </c>
       <c r="G10" s="15">
-        <v>17.23</v>
+        <v>43.89</v>
       </c>
       <c r="H10" s="15">
-        <v>31.4</v>
+        <v>62.54</v>
       </c>
       <c r="I10" s="15">
-        <v>125.13</v>
+        <v>172.96</v>
       </c>
       <c r="J10" s="15">
-        <v>5674.7</v>
+        <v>13514.3</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2115,25 +2115,25 @@
         <v>108</v>
       </c>
       <c r="D11" s="21">
-        <v>7591</v>
+        <v>4238</v>
       </c>
       <c r="E11" s="22" t="s">
         <v>5</v>
       </c>
       <c r="F11" s="21">
-        <v>1.62</v>
+        <v>2.72</v>
       </c>
       <c r="G11" s="21">
-        <v>14.04</v>
+        <v>35.38</v>
       </c>
       <c r="H11" s="21">
-        <v>25.66</v>
+        <v>52.01</v>
       </c>
       <c r="I11" s="21">
-        <v>88.52</v>
+        <v>137.88</v>
       </c>
       <c r="J11" s="21">
-        <v>496.7</v>
+        <v>277.3</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2147,25 +2147,25 @@
         <v>111</v>
       </c>
       <c r="D12" s="15">
-        <v>7359</v>
+        <v>4212</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>5</v>
       </c>
       <c r="F12" s="15">
-        <v>0.64</v>
+        <v>1.43</v>
       </c>
       <c r="G12" s="15">
-        <v>6.61</v>
+        <v>16.61</v>
       </c>
       <c r="H12" s="15">
-        <v>11.85</v>
+        <v>25.11</v>
       </c>
       <c r="I12" s="15">
-        <v>69.93</v>
+        <v>74.87</v>
       </c>
       <c r="J12" s="15">
-        <v>711.5</v>
+        <v>407.2</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2179,25 +2179,25 @@
         <v>113</v>
       </c>
       <c r="D13" s="21">
-        <v>7463</v>
+        <v>4159</v>
       </c>
       <c r="E13" s="22" t="s">
         <v>5</v>
       </c>
       <c r="F13" s="21">
-        <v>0.81</v>
+        <v>1.75</v>
       </c>
       <c r="G13" s="21">
-        <v>6.65</v>
+        <v>16.57</v>
       </c>
       <c r="H13" s="21">
-        <v>12.02</v>
+        <v>25.06</v>
       </c>
       <c r="I13" s="21">
-        <v>69.61</v>
+        <v>108.52</v>
       </c>
       <c r="J13" s="21">
-        <v>1508.6</v>
+        <v>840.7</v>
       </c>
     </row>
   </sheetData>
@@ -2261,10 +2261,10 @@
         <v>100</v>
       </c>
       <c r="D4" s="23">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="E4" s="15">
-        <v>8.9</v>
+        <v>12.9</v>
       </c>
       <c r="F4" s="15">
         <v>0</v>
@@ -2281,10 +2281,10 @@
         <v>100</v>
       </c>
       <c r="D5" s="24">
-        <v>750</v>
+        <v>856</v>
       </c>
       <c r="E5" s="21">
-        <v>13.3</v>
+        <v>12.1</v>
       </c>
       <c r="F5" s="21">
         <v>0</v>
@@ -2301,10 +2301,10 @@
         <v>100</v>
       </c>
       <c r="D6" s="23">
-        <v>1346</v>
+        <v>1123</v>
       </c>
       <c r="E6" s="15">
-        <v>15</v>
+        <v>21.4</v>
       </c>
       <c r="F6" s="15">
         <v>0</v>
@@ -2321,10 +2321,10 @@
         <v>100</v>
       </c>
       <c r="D7" s="24">
-        <v>1586</v>
+        <v>1046</v>
       </c>
       <c r="E7" s="21">
-        <v>21.6</v>
+        <v>36.1</v>
       </c>
       <c r="F7" s="21">
         <v>0</v>
@@ -2341,10 +2341,10 @@
         <v>100</v>
       </c>
       <c r="D8" s="23">
-        <v>1596</v>
+        <v>1140</v>
       </c>
       <c r="E8" s="15">
-        <v>31.6</v>
+        <v>48.7</v>
       </c>
       <c r="F8" s="15">
         <v>0</v>
@@ -2361,10 +2361,10 @@
         <v>100</v>
       </c>
       <c r="D9" s="24">
-        <v>1641</v>
+        <v>1111</v>
       </c>
       <c r="E9" s="21">
-        <v>34.1</v>
+        <v>56.9</v>
       </c>
       <c r="F9" s="21">
         <v>0</v>
@@ -2381,10 +2381,10 @@
         <v>100</v>
       </c>
       <c r="D10" s="23">
-        <v>1696</v>
+        <v>1186</v>
       </c>
       <c r="E10" s="15">
-        <v>33.2</v>
+        <v>54.3</v>
       </c>
       <c r="F10" s="15">
         <v>0</v>
@@ -2401,10 +2401,10 @@
         <v>100</v>
       </c>
       <c r="D11" s="24">
-        <v>1645</v>
+        <v>1203</v>
       </c>
       <c r="E11" s="21">
-        <v>34.6</v>
+        <v>53.1</v>
       </c>
       <c r="F11" s="21">
         <v>0</v>
@@ -2421,10 +2421,10 @@
         <v>100</v>
       </c>
       <c r="D12" s="23">
-        <v>2001</v>
+        <v>1260</v>
       </c>
       <c r="E12" s="15">
-        <v>25.6</v>
+        <v>49.9</v>
       </c>
       <c r="F12" s="15">
         <v>0</v>
@@ -2441,10 +2441,10 @@
         <v>100</v>
       </c>
       <c r="D13" s="24">
-        <v>2444</v>
+        <v>1280</v>
       </c>
       <c r="E13" s="21">
-        <v>18.5</v>
+        <v>48.7</v>
       </c>
       <c r="F13" s="21">
         <v>0</v>
@@ -2461,10 +2461,10 @@
         <v>100</v>
       </c>
       <c r="D14" s="23">
-        <v>2384</v>
+        <v>1166</v>
       </c>
       <c r="E14" s="15">
-        <v>19</v>
+        <v>52.8</v>
       </c>
       <c r="F14" s="15">
         <v>0</v>
@@ -2481,10 +2481,10 @@
         <v>100</v>
       </c>
       <c r="D15" s="24">
-        <v>2545</v>
+        <v>1224</v>
       </c>
       <c r="E15" s="21">
-        <v>16.8</v>
+        <v>51.5</v>
       </c>
       <c r="F15" s="21">
         <v>0</v>
@@ -2501,10 +2501,10 @@
         <v>100</v>
       </c>
       <c r="D16" s="23">
-        <v>2390</v>
+        <v>1276</v>
       </c>
       <c r="E16" s="15">
-        <v>19.4</v>
+        <v>47.9</v>
       </c>
       <c r="F16" s="15">
         <v>0</v>
@@ -2521,10 +2521,10 @@
         <v>100</v>
       </c>
       <c r="D17" s="24">
-        <v>2612</v>
+        <v>1430</v>
       </c>
       <c r="E17" s="21">
-        <v>16.3</v>
+        <v>41.5</v>
       </c>
       <c r="F17" s="21">
         <v>0</v>
@@ -2541,10 +2541,10 @@
         <v>100</v>
       </c>
       <c r="D18" s="23">
-        <v>2638</v>
+        <v>1412</v>
       </c>
       <c r="E18" s="15">
-        <v>16.1</v>
+        <v>42.2</v>
       </c>
       <c r="F18" s="15">
         <v>0</v>
@@ -2561,10 +2561,10 @@
         <v>100</v>
       </c>
       <c r="D19" s="24">
-        <v>2606</v>
+        <v>1478</v>
       </c>
       <c r="E19" s="21">
-        <v>16</v>
+        <v>40.6</v>
       </c>
       <c r="F19" s="21">
         <v>0</v>
@@ -2581,10 +2581,10 @@
         <v>100</v>
       </c>
       <c r="D20" s="23">
-        <v>2679</v>
+        <v>1360</v>
       </c>
       <c r="E20" s="15">
-        <v>15.3</v>
+        <v>45.3</v>
       </c>
       <c r="F20" s="15">
         <v>0</v>
@@ -2601,10 +2601,10 @@
         <v>100</v>
       </c>
       <c r="D21" s="24">
-        <v>2637</v>
+        <v>1416</v>
       </c>
       <c r="E21" s="21">
-        <v>16.1</v>
+        <v>42.8</v>
       </c>
       <c r="F21" s="21">
         <v>0</v>
@@ -2621,10 +2621,10 @@
         <v>100</v>
       </c>
       <c r="D22" s="23">
-        <v>2495</v>
+        <v>1553</v>
       </c>
       <c r="E22" s="15">
-        <v>18.2</v>
+        <v>37.9</v>
       </c>
       <c r="F22" s="15">
         <v>0</v>
@@ -2641,10 +2641,10 @@
         <v>100</v>
       </c>
       <c r="D23" s="24">
-        <v>2832</v>
+        <v>1446</v>
       </c>
       <c r="E23" s="21">
-        <v>14</v>
+        <v>40.7</v>
       </c>
       <c r="F23" s="21">
         <v>0</v>
@@ -2661,10 +2661,10 @@
         <v>100</v>
       </c>
       <c r="D24" s="23">
-        <v>2707</v>
+        <v>1572</v>
       </c>
       <c r="E24" s="15">
-        <v>15.2</v>
+        <v>36.7</v>
       </c>
       <c r="F24" s="15">
         <v>0</v>
@@ -2681,10 +2681,10 @@
         <v>100</v>
       </c>
       <c r="D25" s="24">
-        <v>2858</v>
+        <v>1305</v>
       </c>
       <c r="E25" s="21">
-        <v>13.5</v>
+        <v>47.8</v>
       </c>
       <c r="F25" s="21">
         <v>0</v>
@@ -2701,10 +2701,10 @@
         <v>100</v>
       </c>
       <c r="D26" s="23">
-        <v>2846</v>
+        <v>1341</v>
       </c>
       <c r="E26" s="15">
-        <v>13.9</v>
+        <v>45</v>
       </c>
       <c r="F26" s="15">
         <v>0</v>
@@ -2721,10 +2721,10 @@
         <v>100</v>
       </c>
       <c r="D27" s="24">
-        <v>2323</v>
+        <v>1165</v>
       </c>
       <c r="E27" s="21">
-        <v>20.5</v>
+        <v>54.7</v>
       </c>
       <c r="F27" s="21">
         <v>0</v>
@@ -2741,10 +2741,10 @@
         <v>100</v>
       </c>
       <c r="D28" s="23">
-        <v>2422</v>
+        <v>1443</v>
       </c>
       <c r="E28" s="15">
-        <v>17.1</v>
+        <v>41.7</v>
       </c>
       <c r="F28" s="15">
         <v>0</v>
@@ -2761,10 +2761,10 @@
         <v>100</v>
       </c>
       <c r="D29" s="24">
-        <v>2475</v>
+        <v>1538</v>
       </c>
       <c r="E29" s="21">
-        <v>17.9</v>
+        <v>38.3</v>
       </c>
       <c r="F29" s="21">
         <v>0</v>
@@ -2781,10 +2781,10 @@
         <v>100</v>
       </c>
       <c r="D30" s="23">
-        <v>2366</v>
+        <v>1573</v>
       </c>
       <c r="E30" s="15">
-        <v>19.7</v>
+        <v>37.3</v>
       </c>
       <c r="F30" s="15">
         <v>0</v>
@@ -2801,10 +2801,10 @@
         <v>100</v>
       </c>
       <c r="D31" s="24">
-        <v>2786</v>
+        <v>1479</v>
       </c>
       <c r="E31" s="21">
-        <v>14.2</v>
+        <v>40</v>
       </c>
       <c r="F31" s="21">
         <v>0</v>
@@ -2821,10 +2821,10 @@
         <v>100</v>
       </c>
       <c r="D32" s="23">
-        <v>2618</v>
+        <v>1265</v>
       </c>
       <c r="E32" s="15">
-        <v>16.4</v>
+        <v>46.6</v>
       </c>
       <c r="F32" s="15">
         <v>0</v>
@@ -2841,10 +2841,10 @@
         <v>100</v>
       </c>
       <c r="D33" s="24">
-        <v>2789</v>
+        <v>1411</v>
       </c>
       <c r="E33" s="21">
-        <v>14.3</v>
+        <v>42.6</v>
       </c>
       <c r="F33" s="21">
         <v>0</v>
@@ -2861,10 +2861,10 @@
         <v>100</v>
       </c>
       <c r="D34" s="23">
-        <v>2692</v>
+        <v>1500</v>
       </c>
       <c r="E34" s="15">
-        <v>15.5</v>
+        <v>39.9</v>
       </c>
       <c r="F34" s="15">
         <v>0</v>
@@ -2881,10 +2881,10 @@
         <v>100</v>
       </c>
       <c r="D35" s="24">
-        <v>2860</v>
+        <v>1400</v>
       </c>
       <c r="E35" s="21">
-        <v>13.6</v>
+        <v>44</v>
       </c>
       <c r="F35" s="21">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>100</v>
       </c>
       <c r="D36" s="23">
-        <v>2809</v>
+        <v>1399</v>
       </c>
       <c r="E36" s="15">
-        <v>14</v>
+        <v>43.7</v>
       </c>
       <c r="F36" s="15">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>100</v>
       </c>
       <c r="D37" s="24">
-        <v>2650</v>
+        <v>1313</v>
       </c>
       <c r="E37" s="21">
-        <v>15.8</v>
+        <v>47.2</v>
       </c>
       <c r="F37" s="21">
         <v>0</v>
@@ -2941,10 +2941,10 @@
         <v>100</v>
       </c>
       <c r="D38" s="23">
-        <v>2824</v>
+        <v>1403</v>
       </c>
       <c r="E38" s="15">
-        <v>14</v>
+        <v>43.1</v>
       </c>
       <c r="F38" s="15">
         <v>0</v>
@@ -2961,10 +2961,10 @@
         <v>100</v>
       </c>
       <c r="D39" s="24">
-        <v>2873</v>
+        <v>1436</v>
       </c>
       <c r="E39" s="21">
-        <v>13.3</v>
+        <v>41.8</v>
       </c>
       <c r="F39" s="21">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>100</v>
       </c>
       <c r="D40" s="23">
-        <v>2854</v>
+        <v>1444</v>
       </c>
       <c r="E40" s="15">
-        <v>13.5</v>
+        <v>41.5</v>
       </c>
       <c r="F40" s="15">
         <v>0</v>
@@ -3001,10 +3001,10 @@
         <v>100</v>
       </c>
       <c r="D41" s="24">
-        <v>2739</v>
+        <v>1536</v>
       </c>
       <c r="E41" s="21">
-        <v>14.5</v>
+        <v>38.2</v>
       </c>
       <c r="F41" s="21">
         <v>0</v>
@@ -3021,10 +3021,10 @@
         <v>100</v>
       </c>
       <c r="D42" s="23">
-        <v>2506</v>
+        <v>1459</v>
       </c>
       <c r="E42" s="15">
-        <v>17.7</v>
+        <v>40.9</v>
       </c>
       <c r="F42" s="15">
         <v>0</v>
@@ -3041,10 +3041,10 @@
         <v>100</v>
       </c>
       <c r="D43" s="24">
-        <v>2746</v>
+        <v>1497</v>
       </c>
       <c r="E43" s="21">
-        <v>14.8</v>
+        <v>39.9</v>
       </c>
       <c r="F43" s="21">
         <v>0</v>
@@ -3061,10 +3061,10 @@
         <v>100</v>
       </c>
       <c r="D44" s="23">
-        <v>2468</v>
+        <v>1459</v>
       </c>
       <c r="E44" s="15">
-        <v>18.5</v>
+        <v>41.3</v>
       </c>
       <c r="F44" s="15">
         <v>0</v>
@@ -3081,10 +3081,10 @@
         <v>100</v>
       </c>
       <c r="D45" s="24">
-        <v>2688</v>
+        <v>1350</v>
       </c>
       <c r="E45" s="21">
-        <v>15.5</v>
+        <v>45</v>
       </c>
       <c r="F45" s="21">
         <v>0</v>
@@ -3101,10 +3101,10 @@
         <v>100</v>
       </c>
       <c r="D46" s="23">
-        <v>2829</v>
+        <v>1045</v>
       </c>
       <c r="E46" s="15">
-        <v>13.8</v>
+        <v>62.8</v>
       </c>
       <c r="F46" s="15">
         <v>0</v>
@@ -3121,10 +3121,10 @@
         <v>100</v>
       </c>
       <c r="D47" s="24">
-        <v>2699</v>
+        <v>1405</v>
       </c>
       <c r="E47" s="21">
-        <v>15</v>
+        <v>43.1</v>
       </c>
       <c r="F47" s="21">
         <v>0</v>
@@ -3141,10 +3141,10 @@
         <v>100</v>
       </c>
       <c r="D48" s="23">
-        <v>2674</v>
+        <v>1380</v>
       </c>
       <c r="E48" s="15">
-        <v>15.3</v>
+        <v>43.4</v>
       </c>
       <c r="F48" s="15">
         <v>0</v>
@@ -3161,10 +3161,10 @@
         <v>100</v>
       </c>
       <c r="D49" s="24">
-        <v>2602</v>
+        <v>1235</v>
       </c>
       <c r="E49" s="21">
-        <v>16.4</v>
+        <v>50.5</v>
       </c>
       <c r="F49" s="21">
         <v>0</v>
@@ -3181,10 +3181,10 @@
         <v>100</v>
       </c>
       <c r="D50" s="23">
-        <v>2857</v>
+        <v>1100</v>
       </c>
       <c r="E50" s="15">
-        <v>13.6</v>
+        <v>58.2</v>
       </c>
       <c r="F50" s="15">
         <v>0</v>
@@ -3201,10 +3201,10 @@
         <v>100</v>
       </c>
       <c r="D51" s="24">
-        <v>2869</v>
+        <v>1237</v>
       </c>
       <c r="E51" s="21">
-        <v>13.4</v>
+        <v>50.4</v>
       </c>
       <c r="F51" s="21">
         <v>0</v>
@@ -3221,10 +3221,10 @@
         <v>100</v>
       </c>
       <c r="D52" s="23">
-        <v>2743</v>
+        <v>1443</v>
       </c>
       <c r="E52" s="15">
-        <v>14.7</v>
+        <v>40.8</v>
       </c>
       <c r="F52" s="15">
         <v>0</v>
@@ -3241,10 +3241,10 @@
         <v>100</v>
       </c>
       <c r="D53" s="24">
-        <v>2587</v>
+        <v>1420</v>
       </c>
       <c r="E53" s="21">
-        <v>16.7</v>
+        <v>42.2</v>
       </c>
       <c r="F53" s="21">
         <v>0</v>
@@ -3261,10 +3261,10 @@
         <v>100</v>
       </c>
       <c r="D54" s="23">
-        <v>2881</v>
+        <v>1579</v>
       </c>
       <c r="E54" s="15">
-        <v>13.3</v>
+        <v>36.2</v>
       </c>
       <c r="F54" s="15">
         <v>0</v>
@@ -3281,10 +3281,10 @@
         <v>100</v>
       </c>
       <c r="D55" s="24">
-        <v>2837</v>
+        <v>1509</v>
       </c>
       <c r="E55" s="21">
-        <v>14</v>
+        <v>38.8</v>
       </c>
       <c r="F55" s="21">
         <v>0</v>
@@ -3301,10 +3301,10 @@
         <v>100</v>
       </c>
       <c r="D56" s="23">
-        <v>2839</v>
+        <v>1592</v>
       </c>
       <c r="E56" s="15">
-        <v>13.6</v>
+        <v>35.6</v>
       </c>
       <c r="F56" s="15">
         <v>0</v>
@@ -3321,10 +3321,10 @@
         <v>100</v>
       </c>
       <c r="D57" s="24">
-        <v>2796</v>
+        <v>1508</v>
       </c>
       <c r="E57" s="21">
-        <v>14.3</v>
+        <v>38.9</v>
       </c>
       <c r="F57" s="21">
         <v>0</v>
@@ -3341,10 +3341,10 @@
         <v>100</v>
       </c>
       <c r="D58" s="23">
-        <v>2187</v>
+        <v>1400</v>
       </c>
       <c r="E58" s="15">
-        <v>22.5</v>
+        <v>43.3</v>
       </c>
       <c r="F58" s="15">
         <v>0</v>
@@ -3361,10 +3361,10 @@
         <v>100</v>
       </c>
       <c r="D59" s="24">
-        <v>2572</v>
+        <v>1548</v>
       </c>
       <c r="E59" s="21">
-        <v>16.9</v>
+        <v>37.5</v>
       </c>
       <c r="F59" s="21">
         <v>0</v>
@@ -3381,10 +3381,10 @@
         <v>100</v>
       </c>
       <c r="D60" s="23">
-        <v>2481</v>
+        <v>1505</v>
       </c>
       <c r="E60" s="15">
-        <v>18.1</v>
+        <v>39.1</v>
       </c>
       <c r="F60" s="15">
         <v>0</v>
@@ -3401,10 +3401,10 @@
         <v>100</v>
       </c>
       <c r="D61" s="24">
-        <v>2460</v>
+        <v>1564</v>
       </c>
       <c r="E61" s="21">
-        <v>18.3</v>
+        <v>36.8</v>
       </c>
       <c r="F61" s="21">
         <v>0</v>
@@ -3421,10 +3421,10 @@
         <v>100</v>
       </c>
       <c r="D62" s="23">
-        <v>2322</v>
+        <v>1469</v>
       </c>
       <c r="E62" s="15">
-        <v>20.5</v>
+        <v>40.9</v>
       </c>
       <c r="F62" s="15">
         <v>0</v>
@@ -3481,7 +3481,7 @@
         <v>187</v>
       </c>
       <c r="C4" s="15">
-        <v>149800</v>
+        <v>84455</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>188</v>
